--- a/out/MLP_Base_repeat_4_000001.xlsx
+++ b/out/MLP_Base_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003719179150884738</v>
+        <v>-0.0002943019607702736</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1601369489295785</v>
+        <v>0.1267178795703224</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.320701476007889</v>
+        <v>0.2537739356581026</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6186945500399336</v>
+        <v>0.4895773565666943</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.398362924732703</v>
+        <v>1.106536475653377</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1903134028037926</v>
+        <v>0.1505972483212504</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.159512984370809</v>
+        <v>0.917532195259691</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03861600510343555</v>
+        <v>0.03055709535984692</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.046133258814228</v>
+        <v>0.8278139564481205</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03344317662633296</v>
+        <v>0.02646416041534731</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.074361219351965</v>
+        <v>0.850150987053171</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01634961004804504</v>
+        <v>0.01293737758466283</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.729251253104852</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.073574108204354</v>
+        <v>0.8495281459893003</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007801917104176527</v>
+        <v>0.006172914716297172</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.729251253104852</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.072807640797419</v>
+        <v>0.8489205926820801</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003247301006163597</v>
+        <v>0.00256867126865702</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.729251253104852</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.071491251091848</v>
+        <v>0.8478779277208203</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002249052422366302</v>
+        <v>0.001778332813450368</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.072739325356185</v>
+        <v>0.8488643641839518</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009363033415736485</v>
+        <v>0.0007397957993560148</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.729251253104852</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.072359656799915</v>
+        <v>0.8485629118560614</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004827652761082561</v>
+        <v>0.0003812031912199617</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.729251253104852</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.072388571870699</v>
+        <v>0.8485847462246033</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001865753915543348</v>
+        <v>0.0001466857209841172</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.072278239935772</v>
+        <v>0.8484964600230672</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.979188682446767e-05</v>
+        <v>7.745918963236801e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.072290509205415</v>
+        <v>0.8485050967831237</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.638512762913345e-05</v>
+        <v>3.565636471755614e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.072283934381445</v>
+        <v>0.8484988491042599</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.950997831750072e-05</v>
+        <v>1.41817221615223e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.072275944083872</v>
+        <v>0.8484914769869991</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.606952625195229e-06</v>
+        <v>3.301093358848441e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.07226761756338</v>
+        <v>0.8484838018832852</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-1.279375894546688e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.072261505515774</v>
+        <v>0.8484778833304143</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.410678356938051e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.072255351801473</v>
+        <v>0.8484719219018297</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.07224953629932</v>
+        <v>0.8484662427251216</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.07224465500107</v>
+        <v>0.8484613614268722</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.072239733799522</v>
+        <v>0.8484564402253244</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.072239725828428</v>
+        <v>0.84845643225423</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.072239885250317</v>
+        <v>0.848456591676119</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8484564960229856</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.07224014032534</v>
+        <v>0.8484568467511419</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.072239893221412</v>
+        <v>0.8484565996472134</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.072239853365939</v>
+        <v>0.8484565597917412</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8484564960229856</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.072239861337034</v>
+        <v>0.8484565677628356</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8484564960229856</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.329251253104851</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.072239893221412</v>
+        <v>0.8484565996472134</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.072239988874545</v>
+        <v>0.8484566953003472</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.072239925105789</v>
+        <v>0.8484566315315913</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.072239885250317</v>
+        <v>0.848456591676119</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.072239861337034</v>
+        <v>0.8484565677628356</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.072239614233106</v>
+        <v>0.8484563206589075</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.072239534522161</v>
+        <v>0.8484562409479628</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.072239582348728</v>
+        <v>0.8484562887745295</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.072239701915145</v>
+        <v>0.8484564083409465</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.072239685972956</v>
+        <v>0.8484563923987576</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.072239701915145</v>
+        <v>0.8484564083409465</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.072239685972956</v>
+        <v>0.8484563923987576</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.072239741770617</v>
+        <v>0.8484564481964189</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.072239741770617</v>
+        <v>0.8484564481964189</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.072239741770617</v>
+        <v>0.8484564481964189</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.072239893221412</v>
+        <v>0.8484565996472134</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.329251253104851</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.072240108440962</v>
+        <v>0.8484568148667641</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.072240020758923</v>
+        <v>0.848456727184725</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.072239972932356</v>
+        <v>0.8484566793581583</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.072240020758923</v>
+        <v>0.848456727184725</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.072239837423751</v>
+        <v>0.8484565438495523</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.072239845394845</v>
+        <v>0.8484565518206467</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.072239853365939</v>
+        <v>0.8484565597917412</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.072239861337034</v>
+        <v>0.8484565677628356</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.072239861337034</v>
+        <v>0.8484565677628356</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.072239901192506</v>
+        <v>0.8484566076183079</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.072239964961262</v>
+        <v>0.8484566713870638</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.072240076556584</v>
+        <v>0.8484567829823861</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.072240124383151</v>
+        <v>0.848456830808953</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.072240084527679</v>
+        <v>0.8484567909534806</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.778954327415217</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.072240012787829</v>
+        <v>0.8484567192136305</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.072240132354245</v>
+        <v>0.8484568387800474</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.072239972932356</v>
+        <v>0.8484566793581583</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.072239741770617</v>
+        <v>0.8484564481964189</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.07223969394405</v>
+        <v>0.848456400369852</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.072239725828428</v>
+        <v>0.84845643225423</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8484564960229856</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8484564960229856</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.072239709886239</v>
+        <v>0.8484564163120409</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.072239590319822</v>
+        <v>0.848456296745624</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.07223955046435</v>
+        <v>0.8484562568901517</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.07223969394405</v>
+        <v>0.848456400369852</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.072239829452656</v>
+        <v>0.8484565358784578</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.072239813510467</v>
+        <v>0.8484565199362689</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8484564960229856</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.072239749741711</v>
+        <v>0.8484564561675133</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.072239646117483</v>
+        <v>0.8484563525432853</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.072239526551066</v>
+        <v>0.8484562329768682</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.072239646117483</v>
+        <v>0.8484563525432853</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.6427816135952729</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.07223969394405</v>
+        <v>0.848456400369852</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8484564960229856</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-1.242781613595273</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.072239670030767</v>
+        <v>0.8484563764565687</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981236</v>
+        <v>2.378954327415217</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.072239678001861</v>
+        <v>0.8484563844276631</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_4_000001.xlsx
+++ b/out/MLP_Base_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534075</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962525</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962525</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962525</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003719179150884738</v>
+        <v>-0.0002827243120346684</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1601369489295785</v>
+        <v>0.1217328801691871</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.320701476007889</v>
+        <v>0.2437906332104213</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6186945500399336</v>
+        <v>0.4703176675469189</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.398362924732703</v>
+        <v>1.063006046647524</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1903134028037926</v>
+        <v>0.1446723510027055</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.159512984370809</v>
+        <v>0.8814370609394235</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03861600510343555</v>
+        <v>0.0293553027498044</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.046133258814228</v>
+        <v>0.7952479697335251</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03344317662633296</v>
+        <v>0.02542299681573856</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>3.329251253104851</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.074361219351965</v>
+        <v>0.8167062079331368</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01634961004804504</v>
+        <v>0.01242872615942623</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.729251253104852</v>
+        <v>2.237200859271899</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.073574108204354</v>
+        <v>0.8161078700681457</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007801917104176527</v>
+        <v>0.005929700249854153</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.729251253104852</v>
+        <v>2.037200859271898</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.072807640797419</v>
+        <v>0.8155240383057911</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003247301006163597</v>
+        <v>0.002467350011703618</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.729251253104852</v>
+        <v>1.196909249534075</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.071491251091848</v>
+        <v>0.8145222245283834</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002249052422366302</v>
+        <v>0.001708110707857991</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981236</v>
+        <v>1.196909249534075</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.072739325356185</v>
+        <v>0.8154696297785484</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009363033415736485</v>
+        <v>0.0007101585962674536</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.729251253104852</v>
+        <v>1.196909249534075</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.072359656799915</v>
+        <v>0.8151798464590658</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004827652761082561</v>
+        <v>0.0003658352441644961</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.729251253104852</v>
+        <v>1.196909249534075</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.072388571870699</v>
+        <v>0.8152006369372986</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001865753915543348</v>
+        <v>0.0001409122160331646</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962525</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.072278239935772</v>
+        <v>0.8151155207987968</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.979188682446767e-05</v>
+        <v>7.459602332568856e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.072290509205415</v>
+        <v>0.815123637894318</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.638512762913345e-05</v>
+        <v>3.39623495209913e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.072283934381445</v>
+        <v>0.8151174418699446</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.950997831750072e-05</v>
+        <v>1.364889654592446e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.072275944083872</v>
+        <v>0.8151101666435303</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.606952625195229e-06</v>
+        <v>2.839921505579082e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.07226761756338</v>
+        <v>0.8151026361711423</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-1.279375894546688e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.072261505515774</v>
+        <v>0.8150967654448382</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.072255351801473</v>
+        <v>0.8150909006488369</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.07224953629932</v>
+        <v>0.8150852214721288</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.07224465500107</v>
+        <v>0.8150803401738794</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.072239733799522</v>
+        <v>0.8150754189723316</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.072239725828428</v>
+        <v>0.8150754110012371</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.072239885250317</v>
+        <v>0.8150755704231262</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8150754747699928</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.07224014032534</v>
+        <v>0.8150758254981491</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.072239893221412</v>
+        <v>0.8150755783942206</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.072239853365939</v>
+        <v>0.8150755385387484</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8150754747699928</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.072239861337034</v>
+        <v>0.8150755465098428</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.3566176397962525</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8150754747699928</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.072239893221412</v>
+        <v>0.8150755783942206</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.329251253104851</v>
+        <v>1.396909249534075</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.072239988874545</v>
+        <v>0.8150756740473544</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.072239925105789</v>
+        <v>0.8150756102785985</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.072239885250317</v>
+        <v>0.8150755704231262</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.072239861337034</v>
+        <v>0.8150755465098428</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.072239614233106</v>
+        <v>0.8150752994059147</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.072239534522161</v>
+        <v>0.81507521969497</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.072239582348728</v>
+        <v>0.8150752675215367</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.072239701915145</v>
+        <v>0.8150753870879538</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.072239685972956</v>
+        <v>0.8150753711457648</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.072239701915145</v>
+        <v>0.8150753870879538</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.072239685972956</v>
+        <v>0.8150753711457648</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.072239741770617</v>
+        <v>0.8150754269434261</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.072239741770617</v>
+        <v>0.8150754269434261</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.072239741770617</v>
+        <v>0.8150754269434261</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3470245394981236</v>
+        <v>1.396909249534076</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.072239893221412</v>
+        <v>0.8150755783942206</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.072240108440962</v>
+        <v>0.8150757936137712</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3470245394981236</v>
+        <v>0.5566176397962526</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.072240020758923</v>
+        <v>0.8150757059317322</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3470245394981236</v>
+        <v>-0.2836739699415704</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.072239972932356</v>
+        <v>0.8150756581051655</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.072240020758923</v>
+        <v>0.8150757059317322</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.072239837423751</v>
+        <v>0.8150755225965595</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.072239845394845</v>
+        <v>0.8150755305676539</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.072239853365939</v>
+        <v>0.8150755385387484</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.072239861337034</v>
+        <v>0.8150755465098428</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.072239861337034</v>
+        <v>0.8150755465098428</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.072239901192506</v>
+        <v>0.8150755863653152</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.072239964961262</v>
+        <v>0.815075650134071</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.072240076556584</v>
+        <v>0.8150757617293933</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.072240124383151</v>
+        <v>0.8150758095559602</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.072240084527679</v>
+        <v>0.8150757697004879</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.072240012787829</v>
+        <v>0.8150756979606377</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.072240132354245</v>
+        <v>0.8150758175270546</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.072239972932356</v>
+        <v>0.8150756581051655</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.072239741770617</v>
+        <v>0.8150754269434261</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.07223969394405</v>
+        <v>0.8150753791168592</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.072239725828428</v>
+        <v>0.8150754110012371</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8150754747699928</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8150754747699928</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.072239709886239</v>
+        <v>0.8150753950590482</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.072239590319822</v>
+        <v>0.8150752754926311</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.07223955046435</v>
+        <v>0.8150752356371589</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.07223969394405</v>
+        <v>0.8150753791168592</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.072239829452656</v>
+        <v>0.815075514625465</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.072239813510467</v>
+        <v>0.8150754986832761</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8150754747699928</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.072239749741711</v>
+        <v>0.8150754349145205</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.072239646117483</v>
+        <v>0.8150753312902925</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.072239526551066</v>
+        <v>0.8150752117238755</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.072239646117483</v>
+        <v>0.8150753312902925</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.07223969394405</v>
+        <v>0.8150753791168592</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.072239789597184</v>
+        <v>0.8150754747699928</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.072239670030767</v>
+        <v>0.8150753552035759</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981236</v>
+        <v>-0.4836739699415704</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.072239678001861</v>
+        <v>0.8150753631746703</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_4_000001.xlsx
+++ b/out/MLP_Base_repeat_4_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3625978231430054</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4553426802158356</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3828126788139343</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3565117716789246</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.3835670351982117</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4653351604938507</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3491950631141663</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3473974764347076</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.3873911499977112</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.32573002576828</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3616014122962952</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3363932073116302</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.3951407074928284</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4767190515995026</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5566176397962526</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.510445773601532</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.396909249534076</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.5146623849868774</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.396909249534075</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4327954649925232</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5566176397962526</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4479169249534607</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2836739699415704</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.44285848736763</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3845462203025818</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3791183531284332</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4121698141098022</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.452586829662323</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4803453981876373</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4204225838184357</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4102241992950439</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3999221324920654</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3624225258827209</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4081040024757385</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5566176397962525</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5092694759368896</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5566176397962525</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3909328877925873</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5566176397962526</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.432765781879425</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.3637150824069977</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.3558888733386993</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3406603634357452</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.376026839017868</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.3976652920246124</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4176879823207855</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3566176397962525</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5324184894561768</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.396909249534076</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5659195780754089</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.6535738110542297</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6842066049575806</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002827243120346684</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1217328801691871</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.7951756119728088</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.237200859271899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2437906332104213</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4703176675469189</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7980653047561646</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.237200859271899</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.063006046647524</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1446723510027055</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.6583975553512573</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.237200859271899</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8814370609394235</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0293553027498044</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.6497881412506104</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.237200859271899</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7952479697335251</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02542299681573856</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5100550651550293</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.237200859271899</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8167062079331368</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01242872615942623</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5515860915184021</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.237200859271899</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8161078700681457</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005929700249854153</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5134174227714539</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.037200859271898</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8155240383057911</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002467350011703618</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5079775452613831</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.196909249534075</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8145222245283834</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001708110707857991</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4690292179584503</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.196909249534075</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8154696297785484</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007101585962674536</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5646735429763794</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.196909249534075</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8151798464590658</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003658352441644961</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.5721191763877869</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.196909249534075</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8152006369372986</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001409122160331646</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4746299982070923</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.3566176397962525</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8151155207987968</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.459602332568856e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4641294181346893</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.815123637894318</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.39623495209913e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.381538450717926</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8151174418699446</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.364889654592446e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.4144878089427948</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8151101666435303</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.839921505579082e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.4233357012271881</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8151026361711423</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4286735057830811</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8150967654448382</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.4622848927974701</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8150909006488369</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4471102952957153</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8150852214721288</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4845283925533295</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8150803401738794</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4271178245544434</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8150754189723316</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.4942035377025604</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8150754110012371</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.4593712687492371</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5566176397962526</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8150755704231262</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5492227673530579</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5566176397962526</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8150754747699928</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4951236248016357</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5566176397962526</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8150758254981491</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.461671382188797</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8150755783942206</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4899322986602783</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8150755385387484</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4214980900287628</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8150754747699928</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4253660440444946</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8150755465098428</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4339768588542938</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.3566176397962525</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8150754747699928</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.6716976761817932</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.396909249534076</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8150755783942206</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5492407083511353</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.396909249534075</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8150756740473544</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4390697181224823</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5566176397962526</v>
+        <v>0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8150756102785985</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3867668509483337</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8150755704231262</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4746273756027222</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8150755465098428</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4327174127101898</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8150752994059147</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3926345109939575</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.81507521969497</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4003481268882751</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8150752675215367</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3707753419876099</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8150753870879538</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4154570400714874</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8150753711457648</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4055110812187195</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8150753870879538</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4246759116649628</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8150753711457648</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4085789918899536</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8150754269434261</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.363579273223877</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5566176397962526</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8150754269434261</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.5003852844238281</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5566176397962526</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8150754269434261</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3998538851737976</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.396909249534076</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8150755783942206</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.528275728225708</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5566176397962526</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8150757936137712</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3949838876724243</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5566176397962526</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8150757059317322</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4039353728294373</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2836739699415704</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8150756581051655</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4364831745624542</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8150757059317322</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.379023402929306</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8150755225965595</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3761495351791382</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8150755305676539</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4115161895751953</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8150755385387484</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3607321083545685</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8150755465098428</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3659610152244568</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8150755465098428</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4860796630382538</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8150755863653152</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4500872492790222</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.815075650134071</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4584681391716003</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8150757617293933</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3965975642204285</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8150758095559602</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4345857501029968</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8150757697004879</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.448123961687088</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8150756979606377</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.4494392871856689</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8150758175270546</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4917788505554199</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8150756581051655</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.429236888885498</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8150754269434261</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4235832989215851</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8150753791168592</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3753361999988556</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8150754110012371</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.416412740945816</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8150754747699928</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3695047497749329</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8150754747699928</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3779752850532532</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8150753950590482</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3992083668708801</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8150752754926311</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3933005630970001</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8150752356371589</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4176464676856995</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8150753791168592</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3903931379318237</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.815075514625465</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.360226035118103</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8150754986832761</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3823524117469788</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8150754747699928</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3907638192176819</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8150754349145205</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4513451457023621</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8150753312902925</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.48753821849823</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8150752117238755</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4035655558109283</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8150753312902925</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4346975088119507</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8150753791168592</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.381364494562149</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4836739699415704</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8150754747699928</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4032788872718811</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8150753552035759</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4645314812660217</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4836739699415704</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8150753631746703</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>
